--- a/data/trans_dic/P16-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,33; 45,11</t>
+          <t>36,61; 44,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,55; 56,21</t>
+          <t>48,31; 56,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,3; 53,93</t>
+          <t>46,37; 54,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,83; 60,1</t>
+          <t>50,87; 59,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,38; 60,76</t>
+          <t>53,88; 61,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,99; 72,42</t>
+          <t>65,11; 72,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,81; 71,1</t>
+          <t>63,97; 70,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,37; 67,44</t>
+          <t>61,59; 67,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,21; 51,43</t>
+          <t>45,98; 51,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,72; 63,42</t>
+          <t>57,58; 63,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,0; 61,36</t>
+          <t>56,3; 61,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,31; 62,72</t>
+          <t>57,33; 63,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,15; 44,76</t>
+          <t>37,92; 44,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,77; 53,43</t>
+          <t>46,64; 52,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,52; 52,07</t>
+          <t>45,91; 52,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 48,29</t>
+          <t>17,19; 48,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,94; 62,38</t>
+          <t>56,2; 62,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,16; 73,95</t>
+          <t>68,13; 74,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,15; 68,02</t>
+          <t>62,14; 68,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,78; 66,13</t>
+          <t>60,84; 66,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,07; 52,8</t>
+          <t>47,89; 52,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,24; 62,7</t>
+          <t>58,4; 62,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,85; 59,4</t>
+          <t>55,2; 59,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,15; 56,11</t>
+          <t>33,01; 56,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,23; 43,08</t>
+          <t>35,58; 42,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,93; 51,67</t>
+          <t>43,81; 51,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,78; 50,62</t>
+          <t>42,52; 50,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,35; 58,26</t>
+          <t>49,65; 58,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,99; 62,28</t>
+          <t>54,26; 61,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,26; 71,34</t>
+          <t>64,36; 71,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,42; 64,77</t>
+          <t>58,04; 64,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55,81; 82,66</t>
+          <t>55,39; 83,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,68; 51,17</t>
+          <t>46,0; 51,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,17; 60,5</t>
+          <t>55,19; 60,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,41; 56,49</t>
+          <t>51,47; 56,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,12; 75,75</t>
+          <t>54,42; 74,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,64; 43,49</t>
+          <t>37,43; 43,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,49; 54,99</t>
+          <t>48,58; 54,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,68; 56,26</t>
+          <t>49,96; 56,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,01; 60,41</t>
+          <t>52,99; 60,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,37; 62,68</t>
+          <t>56,12; 62,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,69; 75,17</t>
+          <t>69,44; 75,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,99; 68,28</t>
+          <t>61,89; 68,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,32; 75,3</t>
+          <t>65,36; 74,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,43; 52,81</t>
+          <t>48,41; 52,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,24; 64,85</t>
+          <t>60,52; 65,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,34; 61,88</t>
+          <t>57,14; 61,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,68; 68,3</t>
+          <t>60,64; 67,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,87; 42,28</t>
+          <t>39,03; 42,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,74; 52,14</t>
+          <t>48,51; 52,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,13; 51,57</t>
+          <t>48,07; 51,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,87; 53,75</t>
+          <t>38,23; 53,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,74; 60,35</t>
+          <t>56,87; 60,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,64; 71,83</t>
+          <t>68,7; 71,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,99; 66,46</t>
+          <t>63,38; 66,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,35; 73,24</t>
+          <t>63,1; 71,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,45; 50,88</t>
+          <t>48,47; 50,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,2; 61,66</t>
+          <t>59,37; 61,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,35; 58,79</t>
+          <t>56,3; 58,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,05; 61,46</t>
+          <t>51,84; 61,58</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>258725; 312582</t>
+          <t>253717; 307990</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>340612; 394353</t>
+          <t>338937; 392947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312436; 363926</t>
+          <t>312935; 364983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323015; 381888</t>
+          <t>323267; 379813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>367467; 418247</t>
+          <t>370894; 420607</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>452992; 504819</t>
+          <t>453874; 502254</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>429341; 478379</t>
+          <t>430425; 476475</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>414720; 455743</t>
+          <t>416201; 457304</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>638373; 710451</t>
+          <t>635208; 716449</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>807281; 886986</t>
+          <t>805389; 881292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754722; 826914</t>
+          <t>758747; 831067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>751465; 822403</t>
+          <t>751674; 826004</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>366905; 430503</t>
+          <t>364683; 425178</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476081; 543865</t>
+          <t>474743; 538942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>465433; 532391</t>
+          <t>469364; 535467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>235913; 576078</t>
+          <t>205005; 573058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>541685; 604069</t>
+          <t>544198; 604257</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>702843; 762490</t>
+          <t>702531; 763497</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>648188; 709344</t>
+          <t>648027; 710939</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>582375; 633618</t>
+          <t>582867; 635321</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>927908; 1019211</t>
+          <t>924367; 1017449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1193450; 1284857</t>
+          <t>1196694; 1283905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1132895; 1226720</t>
+          <t>1139993; 1230340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>713035; 1206982</t>
+          <t>709965; 1208478</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>239071; 292291</t>
+          <t>241441; 291642</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>332337; 390934</t>
+          <t>331464; 389038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324903; 384520</t>
+          <t>322968; 383324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>347733; 410570</t>
+          <t>349892; 411515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>369204; 425884</t>
+          <t>371047; 423097</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>498852; 553797</t>
+          <t>499654; 553213</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>450784; 508444</t>
+          <t>455640; 508034</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>520928; 771556</t>
+          <t>516958; 781719</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>622299; 697164</t>
+          <t>626671; 700510</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>845721; 927334</t>
+          <t>846002; 928736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>794008; 872559</t>
+          <t>795026; 875671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>902956; 1240778</t>
+          <t>891445; 1213294</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>354674; 409779</t>
+          <t>352695; 412156</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>458686; 520141</t>
+          <t>459576; 520177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>465759; 527515</t>
+          <t>468449; 529844</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>491316; 559901</t>
+          <t>491152; 556129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>585489; 651019</t>
+          <t>582916; 648937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>732376; 790027</t>
+          <t>729748; 789640</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>647079; 712726</t>
+          <t>646037; 710804</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>712926; 821802</t>
+          <t>713339; 817322</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>959409; 1046016</t>
+          <t>959012; 1046890</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1202996; 1295036</t>
+          <t>1208467; 1297952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1136024; 1226120</t>
+          <t>1132149; 1220107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1224552; 1378389</t>
+          <t>1223917; 1358646</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1273254; 1384974</t>
+          <t>1278406; 1386547</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1667748; 1784240</t>
+          <t>1659947; 1782840</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1633568; 1750301</t>
+          <t>1631591; 1748531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1310152; 1859567</t>
+          <t>1322592; 1860030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1917351; 2039467</t>
+          <t>1921725; 2034112</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2440594; 2553846</t>
+          <t>2442542; 2556228</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2232652; 2355591</t>
+          <t>2246478; 2364311</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2317771; 2679727</t>
+          <t>2308673; 2627814</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3224177; 3385897</t>
+          <t>3225281; 3389671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4130658; 4301986</t>
+          <t>4142304; 4302665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3910385; 4079246</t>
+          <t>3906636; 4069645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3634249; 4375000</t>
+          <t>3690438; 4383430</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,61; 44,44</t>
+          <t>37,11; 44,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,31; 56,01</t>
+          <t>48,22; 55,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,37; 54,09</t>
+          <t>46,47; 53,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,87; 59,77</t>
+          <t>50,78; 59,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,88; 61,1</t>
+          <t>53,56; 60,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,11; 72,05</t>
+          <t>64,7; 72,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,97; 70,82</t>
+          <t>63,89; 71,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,59; 67,67</t>
+          <t>60,51; 66,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,98; 51,87</t>
+          <t>46,32; 51,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,58; 63,01</t>
+          <t>57,74; 63,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,3; 61,67</t>
+          <t>56,27; 61,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,33; 63,0</t>
+          <t>56,86; 62,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,92; 44,21</t>
+          <t>37,87; 44,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,64; 52,94</t>
+          <t>47,24; 53,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,91; 52,37</t>
+          <t>45,86; 52,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,19; 48,04</t>
+          <t>43,16; 50,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,2; 62,4</t>
+          <t>56,05; 62,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,13; 74,04</t>
+          <t>67,79; 73,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,14; 68,17</t>
+          <t>62,37; 68,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,84; 66,31</t>
+          <t>60,1; 65,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,89; 52,71</t>
+          <t>48,07; 52,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,4; 62,66</t>
+          <t>58,2; 62,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,2; 59,57</t>
+          <t>55,07; 59,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 56,18</t>
+          <t>52,86; 57,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,58; 42,98</t>
+          <t>35,14; 42,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,81; 51,42</t>
+          <t>44,01; 51,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,52; 50,47</t>
+          <t>42,89; 50,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,65; 58,4</t>
+          <t>49,32; 57,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,26; 61,87</t>
+          <t>53,73; 61,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,36; 71,26</t>
+          <t>63,84; 71,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,04; 64,72</t>
+          <t>57,6; 64,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55,39; 83,75</t>
+          <t>56,82; 63,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,0; 51,42</t>
+          <t>45,65; 51,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,19; 60,59</t>
+          <t>55,31; 60,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,47; 56,69</t>
+          <t>51,19; 56,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,42; 74,07</t>
+          <t>54,15; 59,44</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,43; 43,74</t>
+          <t>37,63; 43,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,58; 54,99</t>
+          <t>48,44; 55,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,96; 56,51</t>
+          <t>50,07; 56,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,99; 60,0</t>
+          <t>51,85; 58,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,12; 62,48</t>
+          <t>56,27; 62,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,44; 75,14</t>
+          <t>69,23; 75,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,89; 68,1</t>
+          <t>62,21; 68,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,36; 74,89</t>
+          <t>62,79; 68,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,41; 52,85</t>
+          <t>48,13; 52,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,52; 65,0</t>
+          <t>60,52; 64,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,14; 61,58</t>
+          <t>57,13; 61,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,64; 67,32</t>
+          <t>58,42; 62,78</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,03; 42,33</t>
+          <t>38,75; 42,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,51; 52,1</t>
+          <t>48,61; 52,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,07; 51,51</t>
+          <t>48,05; 51,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,23; 53,76</t>
+          <t>50,34; 54,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,87; 60,2</t>
+          <t>56,82; 60,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,7; 71,9</t>
+          <t>68,7; 71,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,7</t>
+          <t>63,27; 66,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,83</t>
+          <t>61,94; 64,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,47; 50,94</t>
+          <t>48,5; 50,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,37; 61,67</t>
+          <t>59,31; 61,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,3; 58,65</t>
+          <t>56,27; 58,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,84; 61,58</t>
+          <t>56,79; 59,15</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>351154</t>
+          <t>380360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>436992</t>
+          <t>466792</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>788146</t>
+          <t>847153</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>253717; 307990</t>
+          <t>257196; 309976</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>338937; 392947</t>
+          <t>338291; 391622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312935; 364983</t>
+          <t>313585; 363055</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323267; 379813</t>
+          <t>350757; 408681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>370894; 420607</t>
+          <t>368678; 419715</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>453874; 502254</t>
+          <t>450988; 502338</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>430425; 476475</t>
+          <t>429892; 478913</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>416201; 457304</t>
+          <t>443571; 487737</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>635208; 716449</t>
+          <t>639776; 712748</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>805389; 881292</t>
+          <t>807604; 885064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>758747; 831067</t>
+          <t>758331; 832459</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>751674; 826004</t>
+          <t>809646; 884439</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447481</t>
+          <t>489565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>608031</t>
+          <t>675627</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1055512</t>
+          <t>1165191</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>364683; 425178</t>
+          <t>364187; 427178</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>474743; 538942</t>
+          <t>480839; 545184</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>469364; 535467</t>
+          <t>468900; 533207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205005; 573058</t>
+          <t>452740; 527495</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>544198; 604257</t>
+          <t>542806; 604500</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>702531; 763497</t>
+          <t>698982; 759453</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>648027; 710939</t>
+          <t>650470; 712680</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>582867; 635321</t>
+          <t>643533; 702575</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>924367; 1017449</t>
+          <t>927815; 1014905</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1196694; 1283905</t>
+          <t>1192593; 1284972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1139993; 1230340</t>
+          <t>1137448; 1225797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>709965; 1208478</t>
+          <t>1120476; 1210469</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381360</t>
+          <t>426926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>627152</t>
+          <t>490464</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1008512</t>
+          <t>917390</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>241441; 291642</t>
+          <t>238446; 290352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>331464; 389038</t>
+          <t>332942; 390667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>322968; 383324</t>
+          <t>325792; 383796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>349892; 411515</t>
+          <t>396080; 459796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>371047; 423097</t>
+          <t>367427; 419852</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>499654; 553213</t>
+          <t>495609; 552909</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>455640; 508034</t>
+          <t>452165; 508958</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>516958; 781719</t>
+          <t>461528; 516651</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>626671; 700510</t>
+          <t>621955; 696660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>846002; 928736</t>
+          <t>847799; 926477</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>795026; 875671</t>
+          <t>790620; 873269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>891445; 1213294</t>
+          <t>874704; 960079</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525632</t>
+          <t>548448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>750777</t>
+          <t>731693</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1276409</t>
+          <t>1280141</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>352695; 412156</t>
+          <t>354560; 412925</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>459576; 520177</t>
+          <t>458173; 522145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>468449; 529844</t>
+          <t>469422; 527900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>491152; 556129</t>
+          <t>513333; 581059</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>582916; 648937</t>
+          <t>584415; 647611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>729748; 789640</t>
+          <t>727505; 788645</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>646037; 710804</t>
+          <t>649297; 711944</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>713339; 817322</t>
+          <t>701352; 761251</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>959012; 1046890</t>
+          <t>953419; 1042698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1208467; 1297952</t>
+          <t>1208545; 1294219</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1132149; 1220107</t>
+          <t>1131990; 1227054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1223917; 1358646</t>
+          <t>1230893; 1322899</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1278406; 1386547</t>
+          <t>1269227; 1384329</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1659947; 1782840</t>
+          <t>1663558; 1785559</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1631591; 1748531</t>
+          <t>1631125; 1744987</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1322592; 1860030</t>
+          <t>1778416; 1909063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1921725; 2034112</t>
+          <t>1919943; 2033055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2442542; 2556228</t>
+          <t>2442617; 2556595</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2246478; 2364311</t>
+          <t>2242521; 2360411</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2308673; 2627814</t>
+          <t>2312258; 2418038</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3225281; 3389671</t>
+          <t>3227741; 3384674</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4142304; 4302665</t>
+          <t>4138554; 4304306</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3906636; 4069645</t>
+          <t>3904331; 4081280</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3690438; 4383430</t>
+          <t>4126631; 4298084</t>
         </is>
       </c>
     </row>
